--- a/sample_data/07_企业问答Chatbot参考/招标常见问题与标准答案.xlsx
+++ b/sample_data/07_企业问答Chatbot参考/招标常见问题与标准答案.xlsx
@@ -459,17 +459,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>贵公司是否具备铁路工程施工总承包一级资质？</t>
+          <t>贵公司是否具备电子与智能化工程专业承包壹级资质？</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>是，我公司具备铁路工程施工总承包一级资质。</t>
+          <t>是，我公司具备电子与智能化工程专业承包壹级资质。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>企业资质_铁路总承包一级_20301231.docx</t>
+          <t>企业资质_电子智能化壹级_20291219.docx</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -485,17 +485,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>近5年是否有类似铁路项目业绩？</t>
+          <t>近5年是否有类似铁路四电项目业绩？</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>有，我公司近5年完成京沪高铁XX段路基工程等多项类似业绩。</t>
+          <t>有，我公司完成北京地铁12号线电气火灾监控、龙烟市域铁路RTU采购等多项类似业绩。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>业绩_京沪高铁XX段合同_2024.docx</t>
+          <t>业绩_地铁12号线中标通知_2025.docx</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -511,17 +511,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>拟任项目经理是否具备一级建造师（铁路）？</t>
+          <t>拟任项目经理是否具备相关资历？</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>是，拟任项目经理张三持有一级建造师（铁路工程）注册证书。</t>
+          <t>是，拟任项目经理张方恒具备丰富轨道交通四电项目供货与调试经验。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人员_项目经理张三_建造师.docx</t>
+          <t>人员_项目经理张方恒.docx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -646,12 +646,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>有，我公司完成城市地铁XX号线轨道工程。</t>
+          <t>有，我公司完成北京地铁12号线电气火灾监控设备采购项目。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>业绩_地铁XX号线中标通知_2023.docx</t>
+          <t>业绩_地铁12号线中标通知_2025.docx</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
